--- a/data/rs_pinkfloyd.xlsx
+++ b/data/rs_pinkfloyd.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="7BP9EQgEuJeoNIIheu2wl1audpDrZ67dgiy7sI8wBq4="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="DRCjn80YCCy3z67z6xvMLQ+98unglo6IVTabNCR2Lg0="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="190">
   <si>
     <t>article_source</t>
   </si>
@@ -156,6 +156,59 @@
     <t>Wikipedia</t>
   </si>
   <si>
+    <t>Pink Floyd overview</t>
+  </si>
+  <si>
+    <t>Pink Floyd are an English rock band formed in London in 1965. Gaining an early following as one of the first British psychedelic groups, they were distinguished by their extended compositions, sonic experiments, philosophical lyrics, and elaborate live shows. They became a leading band of the progressive rock genre, cited by some as the greatest progressive rock band of all time.
+Pink Floyd were founded in 1965 by Syd Barrett (guitar, lead vocals), Nick Mason (drums), Roger Waters (bass guitar, vocals) and Richard Wright (keyboards, vocals). With Barrett as their main songwriter, they released two hit singles, "Arnold Layne" and "See Emily Play", and the successful debut album The Piper at the Gates of Dawn (all 1967). David Gilmour (guitar, vocals) joined in 1967; Barrett left in 1968 due to deteriorating mental health. While all four members contributed compositions, Waters became the primary lyricist and thematic leader, devising the concepts behind Pink Floyd's most successful albums, The Dark Side of the Moon (1973), Wish You Were Here (1975), Animals (1977) and The Wall (1979). The musical film based on The Wall, Pink Floyd – The Wall (1982), won two BAFTA Awards. Pink Floyd also composed several film scores.
+Following personal tensions, Wright left Pink Floyd in 1981, followed by Waters in 1985. Gilmour and Mason continued as Pink Floyd, rejoined later by Wright. They produced the albums A Momentary Lapse of Reason (1987) and The Division Bell (1994), backed by major tours, before entering a long hiatus. In 2005, all but Barrett reunited for a performance at the global awareness event Live 8. Barrett died in 2006 and Wright in 2008. The last Pink Floyd studio album, The Endless River (2014), was based on unreleased material from the Division Bell recording sessions. In 2022, Gilmour and Mason reformed Pink Floyd to release the song "Hey, Hey, Rise Up!" in protest of the Russian invasion of Ukraine.
+By 2013, Pink Floyd had sold more than 250 million records worldwide, making them one of the best-selling music artists of all time. The Dark Side of the Moon and The Wall were inducted into the Grammy Hall of Fame, and these albums and Wish You Were Here are among the best-selling albums of all time. Four Pink Floyd albums topped the US Billboard 200 and five topped the UK Albums Chart. Their hit singles include "Arnold Layne" (1967), "See Emily Play" (1967), "Money" (1973), "Another Brick in the Wall, Part 2" (1979), "Not Now John" (1983), "On the Turning Away" (1987) and "High Hopes" (1994). Pink Floyd were inducted into the US Rock and Roll Hall of Fame in 1996 and the UK Music Hall of Fame in 2005. In 2008, they were awarded the Polar Music Prize in Sweden for their contribution to modern music.</t>
+  </si>
+  <si>
+    <t>1963–1965: Formation - Preceding the band</t>
+  </si>
+  <si>
+    <t>1963–1965: Formation - Preceding the band. Waters and Mason met while studying architecture at the London Polytechnic at Regent Street. They first played music together in a group formed by fellow students Keith Noble and Clive Metcalfe, with Noble's sister Sheilagh. Richard Wright, a fellow architecture student, joined later that year, and the group became a sextet, Sigma 6. Waters played lead guitar, Mason drums, and Wright rhythm guitar, later moving to keyboards. The band performed at private functions and rehearsed in a tearoom in the basement of the Regent Street Polytechnic. They performed songs by the Searchers and material written by their manager and songwriter, fellow student Ken Chapman.
+In September 1963, Waters and Mason moved into a flat at 39 Stanhope Gardens, Highgate in London, owned by Mike Leonard, a part-time tutor at the nearby Hornsey College of Art and the Regent Street Polytechnic.Mason moved out after the 1964 academic year, and guitarist Bob Klose moved in during September 1964, prompting Waters's switch to bass. Sigma 6 went through several names, including the Meggadeaths, the Abdabs and the Screaming Abdabs, Leonard's Lodgers, and the Spectrum Five, before settling on the Tea Set. In September 1963, as Metcalfe and Noble left to form their own band, guitarist Syd Barrett joined Klose and Waters at Stanhope Gardens. Klose introduced the band to singer Chris Dennis, a technician with the Royal Air Force (RAF). In December 1964, they secured their first recording time, at a studio in West Hampstead, through one of Wright's friends, who let them use some down time free. Wright, who was taking a break from his studies, did not participate in the session. When the RAF assigned Dennis a post in Bahrain in early 1965, Barrett became the band's frontman.Later that year, they became the resident band at the Countdown Club near Kensington High Street in London, where from late night until early morning they played three sets of 90 minutes each. During this period, spurred by the group's need to extend their sets to minimise song repetition, the band realised that "songs could be extended with lengthy solos", wrote Mason.After pressure from his parents and advice from his college tutors, Klose quit the band in mid-1965 and Barrett took over lead guitar.</t>
+  </si>
+  <si>
+    <t>1965–1967: early years - Pink Floyd</t>
+  </si>
+  <si>
+    <t>1965–1967: early years
+The group rebranded as the Pink Floyd Sound in late 1965. Barrett created the name on the spur of the moment when he discovered that another band, also called the Tea Set, were to perform at one of their gigs. The name is derived from the given names of two blues musicians whose Piedmont blues records Barrett had in his collection, Pink Anderson and Floyd Council. By 1966, the group's repertoire consisted mainly of rhythm and blues songs, and they had begun to receive paid bookings, including a performance at the Marquee Club in December 1966, where Peter Jenner, a lecturer at the London School of Economics, noticed them. Jenner was impressed by the sonic effects Barrett and Wright created and, with his business partner and friend Andrew King, became their manager. The pair had little experience in the music industry and used King's inheritance to set up Blackhill Enterprises, purchasing about £1,000 (equivalent to £23,500 in 2023) worth of new instruments and equipment for the band. Around this time, Jenner suggested the band drop the "Sound" from their name.
+Under Jenner and King's guidance, Pink Floyd became part of London's underground music scene, playing at venues including All Saints Hall and the Marquee. While performing at the Countdown Club, the band had experimented with long instrumental excursions, and they began to expand them with rudimentary but effective light shows, projected by coloured slides and domestic lights. Jenner and King's social connections helped gain the band prominent coverage in the Financial Times and an article in the Sunday Times which stated: "At the launching of the new magazine IT the other night a pop group called the Pink Floyd played throbbing music while a series of bizarre coloured shapes flashed on a huge screen behind them ... apparently very psychedelic."
+In 1966, the band strengthened their business relationship with Blackhill Enterprises, becoming equal partners with Jenner and King and the band members each holding a one-sixth share. By late 1966, their set included fewer R&amp;B standards and more Barrett originals, many of which would be included on their first album. While they had significantly increased the frequency of their performances, the band were still not widely accepted. Following a performance at a Catholic youth club, the owner refused to pay them, claiming that their performance was not music. When their management filed suit in a small claims court against the owner of the youth organisation, a local magistrate upheld the owner's decision. The band was much better received at the UFO Club in London, where they began to build a fan base. Barrett's performances were enthusiastic, "leaping around ... madness ... improvisation ... [inspired] to get past his limitations and into areas that were ... very interesting. Which none of the others could do", wrote biographer Nicholas Schaffner.</t>
+  </si>
+  <si>
+    <t>Signing with EMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signing with EMI
+In 1967, Pink Floyd began to attract the attention of the music industry. While in negotiations with record companies, IT co-founder and UFO club manager Joe Boyd and Pink Floyd's booking agent, Bryan Morrison, arranged and funded a recording session at Sound Techniques in Kensington. On 15 February 1967, Pink Floyd signed with EMI, receiving a £5,000 advance (equivalent to £114,600 in 2023). EMI released the band's first single, "Arnold Layne", with the B-side "Candy and a Currant Bun", on 10 March 1967 on its Columbia label. Both tracks were recorded on 29 January 1967. "Arnold Layne"'s references to cross-dressing led to a ban by several radio stations; however, creative manipulation by the retailers who supplied sales figures to the music business meant that the single reached number 20 in the UK.
+EMI-Columbia released Pink Floyd's second single, "See Emily Play", on 16 June 1967. It fared slightly better than "Arnold Layne", peaking at number 6 in the UK. The band performed on the BBC's Look of the Week, where Waters and Barrett, erudite and engaging, faced tough questioning from Hans Keller. They appeared on the BBC's Top of the Pops, a popular programme that controversially required artists to mime their singing and playing. Though Pink Floyd returned for two more performances, by the third, Barrett had begun to unravel, and around this time the band first noticed significant changes in his behaviour. By early 1967, he was regularly using LSD, and Mason described him as "completely distanced from everything going on".
+</t>
+  </si>
+  <si>
+    <t>The Piper at the Gates of Dawn</t>
+  </si>
+  <si>
+    <t>The Piper at the Gates of Dawn. Morrison and EMI producer Norman Smith negotiated Pink Floyd's first recording contract. As part of the deal, the band agreed to record their first album at EMI Studios in London. Mason recalled that the sessions were trouble-free. Smith disagreed, stating that Barrett was unresponsive to his suggestions and constructive criticism. EMI-Columbia released The Piper at the Gates of Dawn in August 1967. The album reached number six, spending 14 weeks on the UK charts. One month later, it was released under the Tower Records label. Pink Floyd continued to draw large crowds at the UFO Club; however, Barrett's mental breakdown was by then causing serious concern. The group initially hoped that his erratic behaviour would be a passing phase, but some were less optimistic, including Jenner and his assistant, June Child, who commented: "I found [Barrett] in the dressing room and he was so ... gone. Roger Waters and I got him on his feet, [and] we got him out to the stage ... The band started to play and Syd just stood there. He had his guitar around his neck and his arms just hanging down".
+Forced to cancel Pink Floyd's appearance at the prestigious National Jazz and Blues Festival, as well as several other shows, King informed the music press that Barrett was suffering from nervous exhaustion. Waters arranged a meeting with psychiatrist R. D. Laing, and though Waters personally drove Barrett to the appointment, Barrett refused to come out of the car. A stay in Formentera with Sam Hutt, a doctor well established in the underground music scene, led to no visible improvement. The band followed a few concert dates in Europe during September with their first tour of the US in October. As the US tour went on, Barrett's condition grew steadily worse. During appearances on the Dick Clark and Pat Boone shows in November, Barrett confounded his hosts by giving terse answers to questions (or not responding at all) and staring into space. He refused to move his lips when it came time to mime "See Emily Play" on Boone's show. After these embarrassing episodes, King ended their US visit and immediately sent them home to London. Soon after their return, they supported Jimi Hendrix during a tour of England; however, Barrett's depression worsened as the tour continued.</t>
+  </si>
+  <si>
+    <t>1967: replacement of Barrett by Gilmour</t>
+  </si>
+  <si>
+    <t>1967: replacement of Barrett by Gilmour. In December 1967, reaching a crisis point with Barrett, Pink Floyd added guitarist David Gilmour as the fifth member. Gilmour already knew Barrett, having studied with him at Cambridge Tech in the early 1960s. The two had performed at lunchtimes together with guitars and harmonicas, and later hitch-hiked and busked their way around the south of France. In 1965, while a member of Joker's Wild, Gilmour had watched the Tea Set.
+Morrison's assistant, Steve O'Rourke, set Gilmour up in a room at O'Rourke's house with a salary of £30 per week (equivalent to £700 in 2023). In January 1968, Blackhill Enterprises announced Gilmour as the band's newest member, intending to continue with Barrett as a nonperforming songwriter. According to Jenner, the group planned that Gilmour would "cover for [Barrett's] eccentricities". When this proved unworkable, it was decided that Barrett would just write material. In an expression of his frustration, Barrett, who was expected to write additional hit singles to follow up "Arnold Layne" and "See Emily Play", instead introduced "Have You Got It Yet?" to the band, intentionally changing the structure on each performance so as to make the song impossible to follow and learn. In a January 1968 photoshoot of Pink Floyd, the photographs show Barrett looking detached from the others, staring into the distance.
+Working with Barrett eventually proved too difficult, and matters came to a conclusion in January while en route to a performance in Southampton when a band member asked if they should collect Barrett. According to Gilmour, the answer was "Nah, let's not bother", signalling the end of Barrett's tenure with Pink Floyd. Waters later said, "He was our friend, but most of the time we now wanted to strangle him". In early March 1968, Pink Floyd met with business partners Jenner and King to discuss the band's future; Barrett agreed to leave. Jenner and King believed Barrett was the creative genius of the band, and decided to represent him and end their relationship with Pink Floyd. Morrison sold his business to NEMS Enterprises, and O'Rourke became the band's personal manager. Blackhill announced Barrett's departure on 6 April 1968. After Barrett's departure, the burden of lyrical composition and creative direction fell mostly on Waters. Initially, Gilmour mimed to Barrett's voice on the group's European TV appearances; however, while playing on the university circuit, they avoided Barrett songs in favour of Waters and Wright material such as "It Would Be So Nice" and "Careful with That Axe, Eugene". Mason said later that Gilmour added greater structure to Pink Floyd's music and that "we became far less difficult to enjoy, I think".</t>
+  </si>
+  <si>
+    <t>A Saucerful of Secrets (1968). In 1968, Pink Floyd returned to Abbey Road Studios to complete their second album, A Saucerful of Secrets, which they had begun in 1967 under Barrett's leadership. The album included Barrett's final contribution to their discography, "Jugband Blues". Waters developed his own songwriting, contributing "Set the Controls for the Heart of the Sun", "Let There Be More Light", and "Corporal Clegg". Wright composed "See-Saw" and "Remember a Day". Norman Smith encouraged them to self-produce their music, and they recorded demos of new material at their houses. With Smith's instruction at Abbey Road, they learned how to use the recording studio to realise their artistic vision. However, Smith remained unconvinced by their music, and when Mason struggled to perform his drum part on "Remember a Day", Smith stepped in as his replacement. Wright recalled Smith's attitude about the sessions, "Norman gave up on the second album ... he was forever saying things like, 'You can't do twenty minutes of this ridiculous noise'". As neither Waters nor Mason could read music, to illustrate the structure of "A Saucerful of Secrets", they invented their own system of notation. Gilmour later described their method as looking "like an architectural diagram".
+Released in June 1968, A Saucerful of Secrets featured a psychedelic cover designed by Storm Thorgerson and Aubrey Powell of Hipgnosis. The first of several Pink Floyd album covers designed by Hipgnosis, it was the second time that EMI permitted one of their groups to contract designers for an album jacket. The release reached number nine, spending 11 weeks on the UK chart. Record Mirror gave the album an overall favourable review, but urged listeners to "forget it as background music to a party". John Peel described a live performance of the title track as "like a religious experience", while NME described the song as "long and boring ... [with] little to warrant its monotonous direction". On the day after the album's UK release, Pink Floyd performed at the first ever free concert in Hyde Park. In July 1968, they made a second visit to the US. Accompanied by the Soft Machine and the Who, it marked Pink Floyd's first major tour. That December, they released "Point Me at the Sky"; no more successful than the two singles they had released since "See Emily Play", it was their last single until "Money" in 1973.</t>
+  </si>
+  <si>
     <t>Ummagumma and Atom Heart Mother</t>
   </si>
   <si>
@@ -186,7 +239,13 @@
     <t>1978–1985: Waters-led era. The Wall (1979). The Wall and Pink Floyd – The Wall. In July 1978, amid a financial crisis caused by negligent investments, Waters presented two ideas for Pink Floyd's next album. The first was a 90-minute demo with the working title Bricks in the Wall; the other later became Waters's first solo album, The Pros and Cons of Hitch Hiking. Although both Mason and Gilmour were initially cautious, they chose the former. Bob Ezrin co-produced and wrote a forty-page script for the new album. Ezrin based the story on the central figure of Pink—a gestalt character inspired by Waters's childhood experiences, the most notable of which was the death of his father in World War II. This first metaphorical brick led to more problems; Pink would become drug-addled and depressed by the music industry, eventually transforming into a megalomaniac, a development inspired partly by the decline of Syd Barrett. At the end of the album, the increasingly fascist audience would watch as Pink tore down the wall, once again becoming a regular and caring person. During the recording of The Wall, the band became dissatisfied with Wright's lack of contribution and fired him. Gilmour said that Wright was dismissed as he "hadn't contributed anything of any value whatsoever to the album—he did very, very little". According to Mason, Wright would sit in on the sessions "without doing anything, just 'being a producer'". Waters said the band agreed that Wright would either have to "have a long battle" or agree to "leave quietly" after the album was finished; Wright accepted the ultimatum and left. The Wall was supported by Pink Floyd's first single since "Money", "Another Brick in the Wall (Part II)", which topped the charts in the US and the UK. The Wall was released on 30 November 1979 and topped the Billboard chart in the US for 15 weeks, reaching number three in the UK. It is tied for sixth most certified album by RIAA, with 23 million certified units sold in the US. The cover, with a stark brick wall and band name, was the first Pink Floyd album cover since The Piper at the Gates of Dawn not designed by Hipgnosis. Gerald Scarfe produced a series of animations for the Wall tour. He also commissioned the construction of large inflatable puppets representing characters from the storyline, including the "Mother", the "Ex-wife" and the "Schoolmaster". Pink Floyd used the puppets during their performances. Relationships within the band reached an all-time low; their four Winnebagos parked in a circle, the doors facing away from the centre. Waters used his own vehicle to arrive at the venue and stayed in different hotels from the rest of the band. Wright returned as a paid musician, making him the only band member to profit from the tour, which lost about $600,000 (US$2,010,835 in 2023 dollars[129]). The Wall was adapted into a film, Pink Floyd – The Wall. The film was conceived as a combination of live concert footage and animated scenes; however, the concert footage proved impractical to film. Alan Parker agreed to direct and took a different approach. The animated sequences remained, but scenes were acted by actors with no dialogue. Waters was screentested but quickly discarded, and they asked Bob Geldof to accept the role of Pink. Geldof was initially dismissive, condemning The Wall's storyline as "bollocks".[177] Eventually won over by the prospect of participation in a significant film and receiving a large payment for his work, Geldof agreed.[178][nb 32] Screened at the Cannes Film Festival in May 1982, Pink Floyd – The Wall premièred in the UK in July 1982.[179][nb 33]</t>
   </si>
   <si>
-    <t>The Final Cut (1983). The Final Cut (album). In 1982, Waters suggested a project with the working title Spare Bricks, originally conceived as the soundtrack album for Pink Floyd – The Wall. With the onset of the Falklands War, Waters changed direction and began writing new material. He saw Margaret Thatcher's response to the invasion of the Falklands as jingoistic and unnecessary, and dedicated the album to his late father. Immediately arguments arose between Waters and Gilmour, who felt that the album should include all new material, rather than recycle songs passed over for The Wall. Waters felt that Gilmour had contributed little to the band's lyrical repertoire. Michael Kamen, a contributor to the orchestral arrangements of The Wall, mediated between the two, also performing the role traditionally occupied by the then-absent Wright. The tension within the band grew. Waters and Gilmour worked independently; however, Gilmour began to feel the strain, sometimes barely maintaining his composure. After a final confrontation, Gilmour's name disappeared from the credit list, reflecting what Waters felt was his lack of songwriting contributions. Though Mason's musical contributions were minimal, he stayed busy recording sound effects for an experimental Holophonic system to be used on the album. With marital problems of his own, he remained a distant figure. Pink Floyd did not use Thorgerson for the cover design, Waters choosing to design the cover himself. Released in March 1983, The Final Cut went straight to number one in the UK and number six in the US. Waters wrote all the lyrics, as well as all the music on the album. Gilmour did not have any material ready for the album and asked Waters to delay the recording until he could write some songs, but Waters refused. Gilmour later commented: "I'm certainly guilty at times of being lazy ... but he wasn't right about wanting to put some duff tracks on The Final Cut." Rolling Stone gave the album five stars, with Kurt Loder calling it "a superlative achievement ... art rock's crowning masterpiece". Loder viewed The Final Cut as "essentially a Roger Waters solo album". Waters's departure and legal battles. Gilmour recorded his second solo album, About Face, in 1984, and used it to express his feelings about a variety of topics, from the murder of John Lennon to his relationship with Waters. He later stated that he used the album to distance himself from Pink Floyd. Soon afterwards, Waters began touring his first solo album, The Pros and Cons of Hitch Hiking (1984).[192] Wright formed Zee with Dave Harris and recorded Identity, which went almost unnoticed upon its release. Mason released his second solo album, Profiles, in August 1985. Gilmour, Mason, Waters and O'Rourke met for dinner in 1984 to discuss their future. Mason and Gilmour left the restaurant thinking that Pink Floyd could continue after Waters had finished The Pros and Cons of Hitch Hiking, noting that they had had several hiatuses before; however, Waters left believing that Mason and Gilmour had accepted that Pink Floyd were finished. Mason said that Waters later saw the meeting as "duplicity rather than diplomacy", and wrote in his memoir: "Clearly, our communication skills were still troublingly nonexistent. We left the restaurant with diametrically opposed views of what had been decided." Following the release of The Pros and Cons of Hitch Hiking, Waters publicly insisted that Pink Floyd would not reunite. He contacted O'Rourke to discuss settling future royalty payments. O'Rourke felt obliged to inform Mason and Gilmour, which angered Waters, who wanted to dismiss him as the band's manager. He terminated his management contract with O'Rourke and employed Peter Rudge to manage his affairs. Waters wrote to EMI and Columbia announcing he had left the band, and asked them to release him from his contractual obligations. Gilmour believed that Waters left to hasten the demise of Pink Floyd. Waters later stated that, by not making new albums, Pink Floyd would be in breach of contract—which would suggest that royalty payments would be suspended—and that the other band members had forced him from the group by threatening to sue him. He went to the High Court in an effort to dissolve the band and prevent the use of the Pink Floyd name, declaring Pink Floyd "a spent force creatively". When Waters's lawyers discovered that the partnership had never been formally confirmed, Waters returned to the High Court in an attempt to obtain a veto over further use of the band's name. Gilmour responded with a press release affirming that Pink Floyd would continue to exist. The sides reached an out-of-court agreement, finalised on Gilmour's houseboat, the Astoria, on Christmas Eve 1987. In 2013, Waters said he regretted the lawsuit and had failed to appreciate that the Pink Floyd name had commercial value independent of the band members.</t>
+    <t xml:space="preserve">The Final Cut (1983). The Final Cut (album). In 1982, Waters suggested a project with the working title Spare Bricks, originally conceived as the soundtrack album for Pink Floyd – The Wall. With the onset of the Falklands War, Waters changed direction and began writing new material. He saw Margaret Thatcher's response to the invasion of the Falklands as jingoistic and unnecessary, and dedicated the album to his late father. Immediately arguments arose between Waters and Gilmour, who felt that the album should include all new material, rather than recycle songs passed over for The Wall. Waters felt that Gilmour had contributed little to the band's lyrical repertoire. Michael Kamen, a contributor to the orchestral arrangements of The Wall, mediated between the two, also performing the role traditionally occupied by the then-absent Wright. The tension within the band grew. Waters and Gilmour worked independently; however, Gilmour began to feel the strain, sometimes barely maintaining his composure. After a final confrontation, Gilmour's name disappeared from the credit list, reflecting what Waters felt was his lack of songwriting contributions. Though Mason's musical contributions were minimal, he stayed busy recording sound effects for an experimental Holophonic system to be used on the album. With marital problems of his own, he remained a distant figure. Pink Floyd did not use Thorgerson for the cover design, Waters choosing to design the cover himself. Released in March 1983, The Final Cut went straight to number one in the UK and number six in the US. Waters wrote all the lyrics, as well as all the music on the album. Gilmour did not have any material ready for the album and asked Waters to delay the recording until he could write some songs, but Waters refused. Gilmour later commented: "I'm certainly guilty at times of being lazy ... but he wasn't right about wanting to put some duff tracks on The Final Cut." Rolling Stone gave the album five stars, with Kurt Loder calling it "a superlative achievement ... art rock's crowning masterpiece". Loder viewed The Final Cut as "essentially a Roger Waters solo album". </t>
+  </si>
+  <si>
+    <t>Waters's departure and legal battles</t>
+  </si>
+  <si>
+    <t>Waters's departure and legal battles. Gilmour recorded his second solo album, About Face, in 1984, and used it to express his feelings about a variety of topics, from the murder of John Lennon to his relationship with Waters. He later stated that he used the album to distance himself from Pink Floyd. Soon afterwards, Waters began touring his first solo album, The Pros and Cons of Hitch Hiking (1984).[192] Wright formed Zee with Dave Harris and recorded Identity, which went almost unnoticed upon its release. Mason released his second solo album, Profiles, in August 1985. Gilmour, Mason, Waters and O'Rourke met for dinner in 1984 to discuss their future. Mason and Gilmour left the restaurant thinking that Pink Floyd could continue after Waters had finished The Pros and Cons of Hitch Hiking, noting that they had had several hiatuses before; however, Waters left believing that Mason and Gilmour had accepted that Pink Floyd were finished. Mason said that Waters later saw the meeting as "duplicity rather than diplomacy", and wrote in his memoir: "Clearly, our communication skills were still troublingly nonexistent. We left the restaurant with diametrically opposed views of what had been decided." Following the release of The Pros and Cons of Hitch Hiking, Waters publicly insisted that Pink Floyd would not reunite. He contacted O'Rourke to discuss settling future royalty payments. O'Rourke felt obliged to inform Mason and Gilmour, which angered Waters, who wanted to dismiss him as the band's manager. He terminated his management contract with O'Rourke and employed Peter Rudge to manage his affairs. Waters wrote to EMI and Columbia announcing he had left the band, and asked them to release him from his contractual obligations. Gilmour believed that Waters left to hasten the demise of Pink Floyd. Waters later stated that, by not making new albums, Pink Floyd would be in breach of contract—which would suggest that royalty payments would be suspended—and that the other band members had forced him from the group by threatening to sue him. He went to the High Court in an effort to dissolve the band and prevent the use of the Pink Floyd name, declaring Pink Floyd "a spent force creatively". When Waters's lawyers discovered that the partnership had never been formally confirmed, Waters returned to the High Court in an attempt to obtain a veto over further use of the band's name. Gilmour responded with a press release affirming that Pink Floyd would continue to exist. The sides reached an out-of-court agreement, finalised on Gilmour's houseboat, the Astoria, on Christmas Eve 1987. In 2013, Waters said he regretted the lawsuit and had failed to appreciate that the Pink Floyd name had commercial value independent of the band members.</t>
   </si>
   <si>
     <t>A Momentary Lapse of Reason (1987)</t>
@@ -204,24 +263,54 @@
     <t>Live Reunion</t>
   </si>
   <si>
-    <t>2005–2006: Live 8 reunion. A concert stage lit by purple lighting. Four men are performing on the stage as a crowd stands in front of it. Behind the men are video screens displaying images of vinyl records. Waters rejoined his former bandmates at Live 8 in Hyde Park, London on 2 July 2005. On 2 July 2005, Waters, Gilmour, Mason, and Wright performed together as Pink Floyd at Live 8, a benefit concert raising awareness about poverty, in Hyde Park, London. It was their first performance together in more than 24 years. The reunion was arranged by the Live 8 organiser, Bob Geldof. After Gilmour declined, Geldof asked Mason, who contacted Waters. About two weeks later, Waters called Gilmour, their first conversation in two years, and the next day Gilmour agreed. In a statement to the press, the band stressed the unimportance of their problems in the context of the Live 8 event. The group planned their setlist at the Connaught hotel in London, followed by three days of rehearsals at Black Island Studios. The sessions were problematic, with disagreements over the style and pace of the songs they were practising; the running order was decided on the eve of the event. At the beginning of their performance of "Wish You Were Here", Waters told the audience: "[It is] quite emotional, standing up here with these three guys after all these years, standing to be counted with the rest of you ... We're doing this for everyone who's not here, and particularly of course for Syd." At the end, Gilmour thanked the audience and started to walk off the stage. Waters called him back, and the band embraced. Images of the embrace were a favourite among Sunday newspapers after Live 8. Waters said: "I don't think any of us came out of the years from 1985 with any credit ... It was a bad, negative time, and I regret my part in that negativity." Though Pink Floyd turned down a contract worth £136 million for a final tour, Waters did not rule out more performances, suggesting it ought to be for a charity event only. However, Gilmour told the Associated Press that a reunion would not happen: "The [Live 8] rehearsals convinced me it wasn't something I wanted to be doing a lot of ... There have been all sorts of farewell moments in people's lives and careers which they have then rescinded, but I think I can fairly categorically say that there won't be a tour or an album again that I take part in. It isn't to do with animosity or anything like that. It's just ... I've been there, I've done it." In February 2006, Gilmour was interviewed for the Italian newspaper La Repubblica, which announced that Pink Floyd had disbanded. Gilmour said that Pink Floyd were "over", citing his advancing age and his preference for working alone. He and Waters repeatedly said that they had no plans to reunite. 2006–2008: deaths of Barrett and Wright: Barrett died on 7 July 2006, at his home in Cambridge, aged 60. His funeral was held at Cambridge Crematorium on 18 July 2006. No Pink Floyd members attended. Wright said: "The band are very naturally upset and sad to hear of Syd Barrett's death. Syd was the guiding light of the early band line-up and leaves a legacy which continues to inspire."Although Barrett had faded into obscurity over the decades, the national press praised him for his contributions to music. On 10 May 2007, Waters, Gilmour, Wright, and Mason performed at the Barrett tribute concert "Madcap's Last Laugh" at the Barbican Centre in London. Gilmour, Wright, and Mason performed the Barrett compositions "Bike" and "Arnold Layne", and Waters performed a solo version of his song "Flickering Flame". Wright died of cancer on 15 September 2008, aged 65.His former bandmates paid tributes to his life and work; Gilmour said that Wright's contributions were often overlooked, and that his "soulful voice and playing were vital, magical components of our most recognised Pink Floyd sound". A week after Wright's death, Gilmour performed "Remember a Day" from A Saucerful of Secrets, written and originally sung by Wright, in tribute on BBC Two's Later... with Jools Holland. The keyboardist Keith Emerson released a statement praising Wright as the "backbone" of Pink Floyd. 2010–2011: further performances and rereleases: In March 2010, Pink Floyd went to the High Court of Justice to prevent EMI selling individual tracks online, arguing that their 1999 contract "prohibits the sale of albums in any configuration other than the original". The judge ruled in their favour, which the Guardian described as a "triumph for artistic integrity" and a "vindication of the album as a creative format". In January 2011, Pink Floyd signed a new five-year contract with EMI that permitted the sale of single downloads. On 10 July 2010, Waters and Gilmour performed together at a charity event for the Hoping Foundation. The event, which raised money for Palestinian children, took place at Kiddington Hall in Oxfordshire, England, with an audience of approximately 200. In return for Waters's appearance at the event, Gilmour performed "Comfortably Numb" at Waters's performance of The Wall at the London O2 Arena on 12 May 2011, singing the choruses and playing the guitar solos. Mason also joined, playing tambourine for "Outside the Wall" with Gilmour on mandolin. On 26 September 2011, Pink Floyd and EMI launched an exhaustive re-release campaign under the title Why Pink Floyd...?, reissuing the back catalogue in newly remastered versions, including "Experience" and "Immersion" multi-disc multi-format editions. The albums were remastered by James Guthrie, co-producer of The Wall. In November 2015, Pink Floyd released a limited edition EP, 1965: Their First Recordings, comprising six songs recorded prior to The Piper at the Gates of Dawn. The Endless River (2014) and Nick Mason's Saucerful of Secrets: In November 2013, Gilmour and Mason revisited recordings made with Wright during the Division Bell sessions to create a new Pink Floyd album. They recruited session musicians to help record new parts and "generally harness studio technology". Waters was not involved. Mason described the album as a tribute to Wright: "I think this record is a good way of recognising a lot of what he does and how his playing was at the heart of the Pink Floyd sound. Listening back to the sessions, it really brought home to me what a special player he was." The Endless River was released in the following year. Though it received mixed reviews, it became the most pre-ordered album of all time on Amazon UK and debuted at number one in several countries. The vinyl edition was the fastest-selling UK vinyl release of 2014 and the fastest-selling since 1997. Gilmour said The Endless River would be Pink Floyd's last album, saying: "I think we have successfully commandeered the best of what there is ... It's a shame, but this is the end." There was no supporting tour, as Gilmour felt it was impossible without Wright. In 2015, Gilmour reiterated that Pink Floyd were "done" and that to reunite without Wright would be wrong. In November 2016, Pink Floyd released a box set, The Early Years 1965–1972, comprising outtakes, live recordings, remixes, and films from their early career. It was followed in December 2019 by The Later Years, compiling Pink Floyd's work after Waters's departure. The set includes a remixed version of A Momentary Lapse of Reason with more contributions by Wright and Mason, and an expanded reissue of the live album Delicate Sound of Thunder. In November 2020, the reissue of Delicate Sound of Thunder was given a standalone release on multiple formats. Pink Floyd's Live at Knebworth 1990 performance, previously released as part of the Later Years box set, was released on CD and vinyl on 30 April. In 2018, Mason formed a new band, Nick Mason's Saucerful of Secrets, to perform Pink Floyd's early material. The band includes Gary Kemp of Spandau Ballet and the longtime Pink Floyd collaborator Guy Pratt. They toured Europe in September 2018 and North America in 2019. Waters joined the band at the New York Beacon Theatre to perform vocals for "Set the Controls for the Heart of the Sun". 2022–present: "Hey, Hey, Rise Up!" and conflicts: Mason said in 2018 that, while he remained close to Gilmour and Waters, the two remained "at loggerheads". A remixed version of Animals was delayed until 2022 after Gilmour and Waters could not agree on the liner notes. In a public statement, Waters accused Gilmour of attempting to steal credit and complained that Gilmour would not allow him to use Pink Floyd's website and social media channels. Rolling Stone noted that the pair seemed "to have hit yet another low point in their relationship". Andriy Khlyvnyuk, whose vocals are featured in "Hey, Hey, Rise Up!". In March 2022, Gilmour and Mason reunited as Pink Floyd, alongside Pratt and the keyboardist Nitin Sawhney, to record the single "Hey, Hey, Rise Up!", protesting Russian's invasion of Ukraine that February. It features vocals by the BoomBox singer Andriy Khlyvnyuk, taken from an Instagram video of Khlyvnyuk singing the 1914 Ukrainian anthem "Oh, the Red Viburnum in the Meadow" in Kyiv. Gilmour described Khlyvnyuk's performance as "a powerful moment that made me want to put it to music". "Hey, Hey, Rise Up!" was released on 8 April, with proceeds going to Ukrainian Humanitarian Relief. Gilmour said the war had inspired him to release new music as Pink Floyd as he felt it was important to raise awareness in support of Ukraine. Asked whether he was considering more Pink Floyd music, Gilmour said the single was a "one-off". Pink Floyd removed music from streaming services in Russia and Belarus. Their work with Waters remained, leading to speculation that Waters had blocked its removal; Gilmour said only that "I was disappointed ... Read into that what you will." Waters refused to condemn Russia's invasion of Ukraine and criticised "Hey, Hey, Rise Up!". Shortly afterwards, Gilmour and his wife, Polly Samson, condemned Waters on Twitter as "a lying, thieving, hypocritical, tax-avoiding, lip-synching, misogynistic, sick-with-envy megalomaniac". In March 2023, Variety reported that Pink Floyd had been seeking to sell their back catalogue for some time, but that this had been hampered by infighting.</t>
+    <t xml:space="preserve">2005–2006: Live 8 reunion. A concert stage lit by purple lighting. Four men are performing on the stage as a crowd stands in front of it. Behind the men are video screens displaying images of vinyl records. Waters rejoined his former bandmates at Live 8 in Hyde Park, London on 2 July 2005. On 2 July 2005, Waters, Gilmour, Mason, and Wright performed together as Pink Floyd at Live 8, a benefit concert raising awareness about poverty, in Hyde Park, London. It was their first performance together in more than 24 years. The reunion was arranged by the Live 8 organiser, Bob Geldof. After Gilmour declined, Geldof asked Mason, who contacted Waters. About two weeks later, Waters called Gilmour, their first conversation in two years, and the next day Gilmour agreed. In a statement to the press, the band stressed the unimportance of their problems in the context of the Live 8 event. The group planned their setlist at the Connaught hotel in London, followed by three days of rehearsals at Black Island Studios. The sessions were problematic, with disagreements over the style and pace of the songs they were practising; the running order was decided on the eve of the event. At the beginning of their performance of "Wish You Were Here", Waters told the audience: "[It is] quite emotional, standing up here with these three guys after all these years, standing to be counted with the rest of you ... We're doing this for everyone who's not here, and particularly of course for Syd." At the end, Gilmour thanked the audience and started to walk off the stage. Waters called him back, and the band embraced. Images of the embrace were a favourite among Sunday newspapers after Live 8. Waters said: "I don't think any of us came out of the years from 1985 with any credit ... It was a bad, negative time, and I regret my part in that negativity." Though Pink Floyd turned down a contract worth £136 million for a final tour, Waters did not rule out more performances, suggesting it ought to be for a charity event only. However, Gilmour told the Associated Press that a reunion would not happen: "The [Live 8] rehearsals convinced me it wasn't something I wanted to be doing a lot of ... There have been all sorts of farewell moments in people's lives and careers which they have then rescinded, but I think I can fairly categorically say that there won't be a tour or an album again that I take part in. It isn't to do with animosity or anything like that. It's just ... I've been there, I've done it." In February 2006, Gilmour was interviewed for the Italian newspaper La Repubblica, which announced that Pink Floyd had disbanded. Gilmour said that Pink Floyd were "over", citing his advancing age and his preference for working alone. He and Waters repeatedly said that they had no plans to reunite. </t>
+  </si>
+  <si>
+    <t>Deaths of Barrett and Wright</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2006–2008: deaths of Barrett and Wright: Barrett died on 7 July 2006, at his home in Cambridge, aged 60. His funeral was held at Cambridge Crematorium on 18 July 2006. No Pink Floyd members attended. Wright said: "The band are very naturally upset and sad to hear of Syd Barrett's death. Syd was the guiding light of the early band line-up and leaves a legacy which continues to inspire."Although Barrett had faded into obscurity over the decades, the national press praised him for his contributions to music. On 10 May 2007, Waters, Gilmour, Wright, and Mason performed at the Barrett tribute concert "Madcap's Last Laugh" at the Barbican Centre in London. Gilmour, Wright, and Mason performed the Barrett compositions "Bike" and "Arnold Layne", and Waters performed a solo version of his song "Flickering Flame". Wright died of cancer on 15 September 2008, aged 65.His former bandmates paid tributes to his life and work; Gilmour said that Wright's contributions were often overlooked, and that his "soulful voice and playing were vital, magical components of our most recognised Pink Floyd sound". A week after Wright's death, Gilmour performed "Remember a Day" from A Saucerful of Secrets, written and originally sung by Wright, in tribute on BBC Two's Later... with Jools Holland. The keyboardist Keith Emerson released a statement praising Wright as the "backbone" of Pink Floyd. </t>
+  </si>
+  <si>
+    <t>Further performances and rereleases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2010–2011: further performances and rereleases: In March 2010, Pink Floyd went to the High Court of Justice to prevent EMI selling individual tracks online, arguing that their 1999 contract "prohibits the sale of albums in any configuration other than the original". The judge ruled in their favour, which the Guardian described as a "triumph for artistic integrity" and a "vindication of the album as a creative format". In January 2011, Pink Floyd signed a new five-year contract with EMI that permitted the sale of single downloads. On 10 July 2010, Waters and Gilmour performed together at a charity event for the Hoping Foundation. The event, which raised money for Palestinian children, took place at Kiddington Hall in Oxfordshire, England, with an audience of approximately 200. In return for Waters's appearance at the event, Gilmour performed "Comfortably Numb" at Waters's performance of The Wall at the London O2 Arena on 12 May 2011, singing the choruses and playing the guitar solos. Mason also joined, playing tambourine for "Outside the Wall" with Gilmour on mandolin. On 26 September 2011, Pink Floyd and EMI launched an exhaustive re-release campaign under the title Why Pink Floyd...?, reissuing the back catalogue in newly remastered versions, including "Experience" and "Immersion" multi-disc multi-format editions. The albums were remastered by James Guthrie, co-producer of The Wall. In November 2015, Pink Floyd released a limited edition EP, 1965: Their First Recordings, comprising six songs recorded prior to The Piper at the Gates of Dawn. </t>
+  </si>
+  <si>
+    <t>The Endless River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Endless River (2014) and Nick Mason's Saucerful of Secrets: In November 2013, Gilmour and Mason revisited recordings made with Wright during the Division Bell sessions to create a new Pink Floyd album. They recruited session musicians to help record new parts and "generally harness studio technology". Waters was not involved. Mason described the album as a tribute to Wright: "I think this record is a good way of recognising a lot of what he does and how his playing was at the heart of the Pink Floyd sound. Listening back to the sessions, it really brought home to me what a special player he was." The Endless River was released in the following year. Though it received mixed reviews, it became the most pre-ordered album of all time on Amazon UK and debuted at number one in several countries. The vinyl edition was the fastest-selling UK vinyl release of 2014 and the fastest-selling since 1997. Gilmour said The Endless River would be Pink Floyd's last album, saying: "I think we have successfully commandeered the best of what there is ... It's a shame, but this is the end." There was no supporting tour, as Gilmour felt it was impossible without Wright. In 2015, Gilmour reiterated that Pink Floyd were "done" and that to reunite without Wright would be wrong. </t>
+  </si>
+  <si>
+    <t>Nick Mason's Saucerful of Secrets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In November 2016, Pink Floyd released a box set, The Early Years 1965–1972, comprising outtakes, live recordings, remixes, and films from their early career. It was followed in December 2019 by The Later Years, compiling Pink Floyd's work after Waters's departure. The set includes a remixed version of A Momentary Lapse of Reason with more contributions by Wright and Mason, and an expanded reissue of the live album Delicate Sound of Thunder. In November 2020, the reissue of Delicate Sound of Thunder was given a standalone release on multiple formats. Pink Floyd's Live at Knebworth 1990 performance, previously released as part of the Later Years box set, was released on CD and vinyl on 30 April. In 2018, Mason formed a new band, Nick Mason's Saucerful of Secrets, to perform Pink Floyd's early material. The band includes Gary Kemp of Spandau Ballet and the longtime Pink Floyd collaborator Guy Pratt. They toured Europe in September 2018 and North America in 2019. Waters joined the band at the New York Beacon Theatre to perform vocals for "Set the Controls for the Heart of the Sun". </t>
+  </si>
+  <si>
+    <t>2022–present</t>
+  </si>
+  <si>
+    <t>2022–present: "Hey, Hey, Rise Up!" and conflicts: Mason said in 2018 that, while he remained close to Gilmour and Waters, the two remained "at loggerheads". A remixed version of Animals was delayed until 2022 after Gilmour and Waters could not agree on the liner notes. In a public statement, Waters accused Gilmour of attempting to steal credit and complained that Gilmour would not allow him to use Pink Floyd's website and social media channels. Rolling Stone noted that the pair seemed "to have hit yet another low point in their relationship". Andriy Khlyvnyuk, whose vocals are featured in "Hey, Hey, Rise Up!". In March 2022, Gilmour and Mason reunited as Pink Floyd, alongside Pratt and the keyboardist Nitin Sawhney, to record the single "Hey, Hey, Rise Up!", protesting Russian's invasion of Ukraine that February. It features vocals by the BoomBox singer Andriy Khlyvnyuk, taken from an Instagram video of Khlyvnyuk singing the 1914 Ukrainian anthem "Oh, the Red Viburnum in the Meadow" in Kyiv. Gilmour described Khlyvnyuk's performance as "a powerful moment that made me want to put it to music". "Hey, Hey, Rise Up!" was released on 8 April, with proceeds going to Ukrainian Humanitarian Relief. Gilmour said the war had inspired him to release new music as Pink Floyd as he felt it was important to raise awareness in support of Ukraine. Asked whether he was considering more Pink Floyd music, Gilmour said the single was a "one-off". Pink Floyd removed music from streaming services in Russia and Belarus. Their work with Waters remained, leading to speculation that Waters had blocked its removal; Gilmour said only that "I was disappointed ... Read into that what you will." Waters refused to condemn Russia's invasion of Ukraine and criticised "Hey, Hey, Rise Up!". Shortly afterwards, Gilmour and his wife, Polly Samson, condemned Waters on Twitter as "a lying, thieving, hypocritical, tax-avoiding, lip-synching, misogynistic, sick-with-envy megalomaniac". In March 2023, Variety reported that Pink Floyd had been seeking to sell their back catalogue for some time, but that this had been hampered by infighting.</t>
   </si>
   <si>
     <t>Band members</t>
   </si>
   <si>
     <t>List of Pink Floyd band members:
- Syd Barrett – lead and rhythm guitars, vocals (1965–1968) (died 2006)
- David Gilmour – lead and rhythm guitars, vocals, bass, keyboards, synthesisers (1967–present)
- Nick Mason – drums, percussion (1965–present)
- Roger Waters – bass, vocals, rhythm guitar, synthesisers (1965–1985; guest in 2005)
- Richard Wright – keyboards, piano, organ, synthesisers, vocals (1965–1981, 1987–2008; session musician earlier in 1987)(died 2008)</t>
+ Syd Barrett: lead and rhythm guitars, vocals (1965–1968) (died 2006)
+ David Gilmour: lead and rhythm guitars, vocals, bass, keyboards, synthesisers (1967–present)
+ Nick Mason: drums, percussion (1965–present)
+ Roger Waters: bass, vocals, rhythm guitar, synthesisers (1965–1985; guest in 2005)
+ Richard Wright: keyboards, piano, organ, synthesisers, vocals (1965–1981, 1987–2008; session musician earlier in 1987)(died 2008)</t>
   </si>
   <si>
     <t>Genres</t>
   </si>
   <si>
-    <t>Genres: Considered one of the UK's first psychedelic music groups, Pink Floyd began their career at the vanguard of London's underground music scene, appearing at UFO Club and its successor Middle Earth. According to Rolling Stone: "By 1967, they had developed an unmistakably psychedelic sound, performing long, loud suitelike compositions that touched on hard rock, blues, country, folk, and electronic music."Released in 1968, the song "Careful with That Axe, Eugene" helped galvanise their reputation as an art rock group. Other genres attributed to the band are space rock, experimental rock, acid rock, proto-prog, experimental pop (while under Barrett), psychedelic pop, and psychedelic rock. O'Neill Surber comments on the music of Pink Floyd: Rarely will you find Floyd dishing up catchy hooks, tunes short enough for air-play, or predictable three-chord blues progressions; and never will you find them spending much time on the usual pop album of romance, partying, or self-hype. Their sonic universe is expansive, intense, and challenging ... Where most other bands neatly fit the songs to the music, the two forming a sort of autonomous and seamless whole complete with memorable hooks, Pink Floyd tends to set lyrics within a broader soundscape that often seems to have a life of its own ... Pink Floyd employs extended, stand-alone instrumentals which are never mere vehicles for showing off virtuoso but are planned and integral parts of the performance. During the late 1960s, the press labelled Pink Floyd's music psychedelic pop, progressive pop and progressive rock; they gained a following as a psychedelic pop group. In 1968, Wright said: "It's hard to see why we were cast as the first British psychedelic group. We never saw ourselves that way ... we realised that we were, after all, only playing for fun ... tied to no particular form of music, we could do whatever we wanted ... the emphasis ... [is] firmly on spontaneity and improvisation." Waters said later: "There wasn't anything 'grand' about it. We were laughable. We were useless. We couldn't play at all so we had to do something stupid and 'experimental' ... Syd was a genius, but I wouldn't want to go back to playing 'Interstellar Overdrive' for hours and hours." Unconstrained by conventional pop formats, Pink Floyd were innovators of progressive rock during the 1970s and ambient music during the 1980s.</t>
+    <t>Genres: Considered one of the UK's first psychedelic music groups, Pink Floyd began their career at the vanguard of London's underground music scene, appearing at UFO Club and its successor Middle Earth. According to Rolling Stone: "By 1967, they had developed an unmistakably psychedelic sound, performing long, loud suitelike compositions that touched on hard rock, blues, country, folk, and electronic music."Released in 1968, the song "Careful with That Axe, Eugene" helped galvanise their reputation as an art rock group. Other genres attributed to the band are space rock, experimental rock, acid rock, proto-prog, experimental pop (while under Barrett), psychedelic pop, and psychedelic rock. O'Neill Surber comments on the music of Pink Floyd: "Rarely will you find Floyd dishing up catchy hooks, tunes short enough for air-play, or predictable three-chord blues progressions; and never will you find them spending much time on the usual pop album of romance, partying, or self-hype. Their sonic universe is expansive, intense, and challenging ... Where most other bands neatly fit the songs to the music, the two forming a sort of autonomous and seamless whole complete with memorable hooks, Pink Floyd tends to set lyrics within a broader soundscape that often seems to have a life of its own ... Pink Floyd employs extended, stand-alone instrumentals which are never mere vehicles for showing off virtuoso but are planned and integral parts of the performance". During the late 1960s, the press labelled Pink Floyd's music psychedelic pop, progressive pop and progressive rock; they gained a following as a psychedelic pop group. In 1968, Wright said: "It's hard to see why we were cast as the first British psychedelic group. We never saw ourselves that way ... we realised that we were, after all, only playing for fun ... tied to no particular form of music, we could do whatever we wanted ... the emphasis ... [is] firmly on spontaneity and improvisation." Waters said later: "There wasn't anything 'grand' about it. We were laughable. We were useless. We couldn't play at all so we had to do something stupid and 'experimental' ... Syd was a genius, but I wouldn't want to go back to playing 'Interstellar Overdrive' for hours and hours." Unconstrained by conventional pop formats, Pink Floyd were innovators of progressive rock during the 1970s and ambient music during the 1980s.</t>
   </si>
   <si>
     <t>Gilmour's guitar work</t>
@@ -263,9 +352,7 @@
     <t>Discography</t>
   </si>
   <si>
-    <t>Discography
- Pink Floyd discography and List of songs recorded by Pink Floyd
- Studio albums
+    <t>Discography - Studio albums:
  The Piper at the Gates of Dawn (1967)
  A Saucerful of Secrets (1968)
  More (1969)
@@ -286,7 +373,7 @@
     <t>Concert tours</t>
   </si>
   <si>
-    <t>Concert tours
+    <t>Pink Floyd Concert tours:
  Pink Floyd live performances
  Pink Floyd World Tour (1968)
  The Man and The Journey Tour (1969)
@@ -717,7 +804,7 @@
     <numFmt numFmtId="164" formatCode="mmmm\ d\,\ yyyy"/>
     <numFmt numFmtId="165" formatCode="d\-mmmm\-yy"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -753,6 +840,10 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <sz val="10.0"/>
       <color rgb="FF1E1E1E"/>
       <name val="Calibri"/>
@@ -784,7 +875,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="22">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -812,15 +903,36 @@
       <alignment vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1036,7 +1148,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="3" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="19.38"/>
+    <col customWidth="1" min="2" max="2" width="12.63"/>
+    <col customWidth="1" min="3" max="3" width="18.38"/>
     <col customWidth="1" min="4" max="4" width="34.88"/>
     <col customWidth="1" min="5" max="6" width="12.63"/>
   </cols>
@@ -1272,12 +1386,12 @@
       <c r="A16" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="4" t="s">
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="13" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1285,753 +1399,909 @@
       <c r="A17" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="1" t="s">
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="12" t="s">
         <v>48</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" s="1" t="s">
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="12" t="s">
         <v>50</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E19" s="1" t="s">
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="12" t="s">
         <v>52</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>53</v>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>54</v>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="4" t="s">
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="4" t="s">
-        <v>67</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="4" t="s">
+      <c r="A30" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="15" t="s">
         <v>69</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="4" t="s">
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E31" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="E31" s="1" t="s">
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="4" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="4" t="s">
+      <c r="E32" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E32" s="1" t="s">
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="4" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="2" t="s">
+      <c r="E33" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E33" s="1" t="s">
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="4" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="4" t="s">
+      <c r="E34" s="15" t="s">
         <v>77</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="4" t="s">
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="E35" s="15" t="s">
         <v>79</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="2" t="s">
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="E36" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="E36" s="1" t="s">
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="18" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="2" t="s">
+      <c r="E37" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="B37" s="12" t="s">
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="C37" s="2"/>
-      <c r="D37" s="12" t="s">
+      <c r="E38" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="E37" s="13" t="s">
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="18" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B38" s="2" t="s">
+      <c r="E39" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2" t="s">
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E40" s="15" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B39" s="2" t="s">
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="E41" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="E39" s="13" t="s">
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="4" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D40" s="2" t="s">
+      <c r="E42" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E40" s="13" t="s">
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="4" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B41" s="2" t="s">
+      <c r="E43" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2" t="s">
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E41" s="13" t="s">
+      <c r="E44" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2" t="s">
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E42" s="13" t="s">
+      <c r="E45" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2" t="s">
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E43" s="13" t="s">
+      <c r="E46" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2" t="s">
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E44" s="13" t="s">
+      <c r="E47" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2" t="s">
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E45" s="13" t="s">
+      <c r="E48" s="15" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2" t="s">
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="E46" s="13" t="s">
+      <c r="E49" s="15" t="s">
         <v>107</v>
-      </c>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E47" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="E48" s="14" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B49" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C49" s="10"/>
-      <c r="D49" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="E49" s="14" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B50" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="C50" s="10"/>
-      <c r="D50" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="E50" s="14" t="s">
-        <v>117</v>
+        <v>108</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="E50" s="20" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B51" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="E51" s="14" t="s">
-        <v>119</v>
+        <v>108</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C52" s="10"/>
-      <c r="D52" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="E52" s="14" t="s">
-        <v>121</v>
+        <v>108</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E52" s="20" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B53" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="E53" s="14" t="s">
-        <v>123</v>
+        <v>108</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E53" s="20" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B54" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E54" s="14" t="s">
-        <v>126</v>
+        <v>108</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E54" s="20" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B55" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="C55" s="10"/>
-      <c r="D55" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="E55" s="14" t="s">
-        <v>128</v>
+        <v>108</v>
+      </c>
+      <c r="B55" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E55" s="20" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B56" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C56" s="10"/>
-      <c r="D56" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="E56" s="14" t="s">
-        <v>130</v>
+        <v>108</v>
+      </c>
+      <c r="B56" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E56" s="20" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B57" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="B57" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E57" s="20" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B58" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E58" s="20" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B59" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C57" s="10"/>
-      <c r="D57" s="10" t="s">
+      <c r="E59" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="E57" s="14" t="s">
+    </row>
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B60" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="10" t="s">
+      <c r="E60" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="B58" s="10" t="s">
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B61" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="C58" s="10"/>
-      <c r="D58" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="E58" s="14" t="s">
+      <c r="C61" s="11"/>
+      <c r="D61" s="11" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="B59" s="10" t="s">
+      <c r="E61" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="C59" s="10"/>
-      <c r="D59" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="E59" s="14" t="s">
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B62" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C62" s="11"/>
+      <c r="D62" s="11" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="B60" s="10" t="s">
+      <c r="E62" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="C60" s="10"/>
-      <c r="D60" s="10" t="s">
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B63" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="E60" s="14" t="s">
+      <c r="C63" s="11"/>
+      <c r="D63" s="11" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="B61" s="10" t="s">
+      <c r="E63" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="C61" s="10"/>
-      <c r="D61" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="E61" s="14" t="s">
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C64" s="11"/>
+      <c r="D64" s="11" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="B62" s="10" t="s">
+      <c r="E64" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="C62" s="10"/>
-      <c r="D62" s="10" t="s">
+    </row>
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="A65" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B65" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C65" s="11"/>
+      <c r="D65" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="E62" s="14" t="s">
+      <c r="E65" s="21" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="B63" s="10" t="s">
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="A66" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C66" s="11"/>
+      <c r="D66" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="C63" s="10"/>
-      <c r="D63" s="10" t="s">
+      <c r="E66" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="E63" s="14" t="s">
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B67" s="11" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="B64" s="10" t="s">
+      <c r="C67" s="11"/>
+      <c r="D67" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="C64" s="10"/>
-      <c r="D64" s="10" t="s">
+      <c r="E67" s="21" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="A68" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E64" s="14" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="10" t="s">
+      <c r="B68" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C68" s="11"/>
+      <c r="D68" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="E68" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="C65" s="10"/>
-      <c r="D65" s="10" t="s">
+    </row>
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="A69" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B69" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C69" s="11"/>
+      <c r="D69" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="E65" s="14" t="s">
+      <c r="E69" s="21" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="B66" s="10" t="s">
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="A70" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B70" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="C66" s="10"/>
-      <c r="D66" s="10" t="s">
+      <c r="C70" s="11"/>
+      <c r="D70" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="E66" s="14" t="s">
+      <c r="E70" s="21" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="B67" s="10" t="s">
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="A71" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="C67" s="14"/>
-      <c r="D67" s="10" t="s">
+      <c r="B71" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="E67" s="14" t="s">
+      <c r="C71" s="11"/>
+      <c r="D71" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E71" s="21" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="10" t="s">
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="A72" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B72" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="B68" s="10" t="s">
+      <c r="C72" s="11"/>
+      <c r="D72" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="E72" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="C68" s="10"/>
-      <c r="D68" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="E68" s="14" t="s">
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="A73" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B73" s="11" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
+      <c r="C73" s="11"/>
+      <c r="D73" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="E73" s="21" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B74" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="C74" s="11"/>
+      <c r="D74" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="E74" s="21" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="A75" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B75" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="C75" s="11"/>
+      <c r="D75" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="E75" s="21" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="A76" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="C76" s="11"/>
+      <c r="D76" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="E76" s="21" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="C77" s="11"/>
+      <c r="D77" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E77" s="21" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="A78" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="B78" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="C78" s="11"/>
+      <c r="D78" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="E78" s="21" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="A79" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="C79" s="11"/>
+      <c r="D79" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="E79" s="21" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="A80" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="C80" s="21"/>
+      <c r="D80" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="E80" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="A81" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B81" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="C81" s="11"/>
+      <c r="D81" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="E81" s="21" t="s">
+        <v>189</v>
+      </c>
+    </row>
     <row r="82" ht="15.75" customHeight="1"/>
     <row r="83" ht="15.75" customHeight="1"/>
     <row r="84" ht="15.75" customHeight="1"/>
@@ -2951,10 +3221,23 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="1003" ht="15.75" customHeight="1"/>
+    <row r="1004" ht="15.75" customHeight="1"/>
+    <row r="1005" ht="15.75" customHeight="1"/>
+    <row r="1006" ht="15.75" customHeight="1"/>
+    <row r="1007" ht="15.75" customHeight="1"/>
+    <row r="1008" ht="15.75" customHeight="1"/>
+    <row r="1009" ht="15.75" customHeight="1"/>
+    <row r="1010" ht="15.75" customHeight="1"/>
+    <row r="1011" ht="15.75" customHeight="1"/>
+    <row r="1012" ht="15.75" customHeight="1"/>
+    <row r="1013" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="B3"/>
